--- a/research/traditional_assets/database/data/malaysia/malaysia_investments_asset_management.xlsx
+++ b/research/traditional_assets/database/data/malaysia/malaysia_investments_asset_management.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ8"/>
+  <dimension ref="A1:AQ13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,46 +588,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.0275</v>
+        <v>0.0107</v>
       </c>
       <c r="E2">
-        <v>0.0983</v>
+        <v>-0.049</v>
       </c>
       <c r="G2">
-        <v>-0.1757135164243404</v>
+        <v>-0.02176776429809359</v>
       </c>
       <c r="H2">
-        <v>-0.1757135164243404</v>
+        <v>-0.02176776429809359</v>
       </c>
       <c r="I2">
-        <v>-0.1119697286908186</v>
+        <v>0.1082775925232181</v>
       </c>
       <c r="J2">
-        <v>-0.1116008668581231</v>
+        <v>0.1081579157146818</v>
       </c>
       <c r="K2">
-        <v>-71.7</v>
+        <v>-47.686</v>
       </c>
       <c r="L2">
-        <v>-1.930533117932149</v>
+        <v>-1.652894280762565</v>
       </c>
       <c r="M2">
-        <v>0.296</v>
+        <v>1.111</v>
       </c>
       <c r="N2">
-        <v>0.001598272138228942</v>
+        <v>0.001564987111042245</v>
       </c>
       <c r="O2">
-        <v>-0.004128312412831241</v>
+        <v>-0.02329824267080485</v>
       </c>
       <c r="P2">
-        <v>0.296</v>
+        <v>1.111</v>
       </c>
       <c r="Q2">
-        <v>0.001598272138228942</v>
+        <v>0.001564987111042245</v>
       </c>
       <c r="R2">
-        <v>-0.004128312412831241</v>
+        <v>-0.02329824267080485</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,73 +636,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>42.908</v>
+        <v>35.664</v>
       </c>
       <c r="V2">
-        <v>0.2316846652267819</v>
+        <v>0.05023735403079264</v>
       </c>
       <c r="W2">
-        <v>-0.07959623323013415</v>
+        <v>0.0008585858585858586</v>
       </c>
       <c r="X2">
-        <v>0.05253776027529754</v>
+        <v>0.08434413796471429</v>
       </c>
       <c r="Y2">
-        <v>-0.1321339935054317</v>
+        <v>-0.08348555210612843</v>
       </c>
       <c r="Z2">
-        <v>0.07395050927331839</v>
+        <v>0.100771959569411</v>
       </c>
       <c r="AA2">
-        <v>-0.01335932300085576</v>
+        <v>-0.06799654866003015</v>
       </c>
       <c r="AB2">
-        <v>0.05244513407276307</v>
+        <v>0.08424107708469629</v>
       </c>
       <c r="AC2">
-        <v>-0.06699956163526022</v>
+        <v>-0.1522772673529186</v>
       </c>
       <c r="AD2">
-        <v>10.745</v>
+        <v>19.189</v>
       </c>
       <c r="AE2">
-        <v>0.08277861788502039</v>
+        <v>0.1009572785257866</v>
       </c>
       <c r="AF2">
-        <v>10.82777861788502</v>
+        <v>19.28995727852579</v>
       </c>
       <c r="AG2">
-        <v>-32.08022138211498</v>
+        <v>-16.37404272147421</v>
       </c>
       <c r="AH2">
-        <v>0.05523593999905239</v>
+        <v>0.02645359079630031</v>
       </c>
       <c r="AI2">
-        <v>0.03289840396746333</v>
+        <v>0.05571751150706224</v>
       </c>
       <c r="AJ2">
-        <v>-0.2095106306427737</v>
+        <v>-0.02360950798532045</v>
       </c>
       <c r="AK2">
-        <v>-0.1120824757011058</v>
+        <v>-0.0527266330077789</v>
       </c>
       <c r="AL2">
-        <v>14.295</v>
+        <v>0.387</v>
       </c>
       <c r="AM2">
-        <v>12.297</v>
+        <v>-0.578</v>
       </c>
       <c r="AN2">
-        <v>-2.833597046413503</v>
+        <v>93.15048543689295</v>
       </c>
       <c r="AO2">
-        <v>-0.2959076600209864</v>
+        <v>7.886304909560722</v>
       </c>
       <c r="AP2">
-        <v>8.459973993173781</v>
+        <v>-79.48564427900082</v>
       </c>
       <c r="AQ2">
-        <v>-0.3439863381312516</v>
+        <v>-5.280276816608996</v>
       </c>
     </row>
     <row r="3">
@@ -713,7 +713,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>OSK Ventures International Berhad (KLSE:OSKVI)</t>
+          <t>Pimpinan Ehsan Berhad (KLSE:PEB)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -721,29 +721,8 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="D3">
-        <v>0.115</v>
-      </c>
-      <c r="E3">
-        <v>0.0983</v>
-      </c>
-      <c r="G3">
-        <v>0.1576011157601116</v>
-      </c>
-      <c r="H3">
-        <v>0.1576011157601116</v>
-      </c>
-      <c r="I3">
-        <v>0.8619246861924685</v>
-      </c>
-      <c r="J3">
-        <v>0.8538615197732486</v>
-      </c>
       <c r="K3">
-        <v>6.14</v>
-      </c>
-      <c r="L3">
-        <v>0.8563458856345886</v>
+        <v>0.325</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -767,73 +746,64 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>1.02</v>
+        <v>13.5</v>
       </c>
       <c r="V3">
-        <v>0.04197530864197531</v>
+        <v>0.6852791878172589</v>
       </c>
       <c r="W3">
-        <v>0.144811320754717</v>
+        <v>0.02044025157232704</v>
       </c>
       <c r="X3">
-        <v>0.05251915534911063</v>
+        <v>0.08434413796471429</v>
       </c>
       <c r="Y3">
-        <v>0.09229216540560634</v>
-      </c>
-      <c r="Z3">
-        <v>0.1749591274005027</v>
-      </c>
-      <c r="AA3">
-        <v>0.1493908664203946</v>
+        <v>-0.06390388639238725</v>
       </c>
       <c r="AB3">
-        <v>0.05241394437167197</v>
-      </c>
-      <c r="AC3">
-        <v>0.09697692204872267</v>
+        <v>0.08424894719578287</v>
       </c>
       <c r="AD3">
-        <v>0.095</v>
+        <v>0.066</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.095</v>
+        <v>0.066</v>
       </c>
       <c r="AG3">
-        <v>-0.925</v>
+        <v>-13.434</v>
       </c>
       <c r="AH3">
-        <v>0.0038942406230785</v>
+        <v>0.003339067084893252</v>
       </c>
       <c r="AI3">
-        <v>0.001967077337198468</v>
+        <v>0.004500204554752489</v>
       </c>
       <c r="AJ3">
-        <v>-0.03957219251336899</v>
+        <v>-2.143951484200447</v>
       </c>
       <c r="AK3">
-        <v>-0.01956636700158646</v>
+        <v>-11.52144082332761</v>
       </c>
       <c r="AL3">
-        <v>0.002</v>
+        <v>0.003</v>
       </c>
       <c r="AM3">
-        <v>0.002</v>
+        <v>-0.323</v>
       </c>
       <c r="AN3">
-        <v>0.01532258064516129</v>
+        <v>1.5</v>
       </c>
       <c r="AO3">
-        <v>3090</v>
+        <v>10</v>
       </c>
       <c r="AP3">
-        <v>-0.1491935483870968</v>
+        <v>-305.3181818181818</v>
       </c>
       <c r="AQ3">
-        <v>3090</v>
+        <v>-0.09287925696594426</v>
       </c>
     </row>
     <row r="4">
@@ -844,7 +814,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Kuchai Development Berhad (KLSE:KUCHAI)</t>
+          <t>AME Real Estate Investment Trust (KLSE:AMEREIT)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -852,113 +822,92 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="D4">
-        <v>-0.0343</v>
-      </c>
       <c r="G4">
-        <v>1.223564954682779</v>
+        <v>0</v>
       </c>
       <c r="H4">
-        <v>1.223564954682779</v>
+        <v>0</v>
       </c>
       <c r="I4">
-        <v>0.8731117824773414</v>
+        <v>0.7921146953405018</v>
       </c>
       <c r="J4">
-        <v>0.864021851591276</v>
+        <v>0.7921146953405018</v>
       </c>
       <c r="K4">
-        <v>3.62</v>
+        <v>6.4</v>
       </c>
       <c r="L4">
-        <v>1.093655589123867</v>
+        <v>0.7646356033452809</v>
       </c>
       <c r="M4">
-        <v>0.296</v>
+        <v>-0</v>
       </c>
       <c r="N4">
-        <v>0.005532710280373832</v>
+        <v>-0</v>
       </c>
       <c r="O4">
-        <v>0.08176795580110496</v>
+        <v>-0</v>
       </c>
       <c r="P4">
-        <v>0.296</v>
+        <v>-0</v>
       </c>
       <c r="Q4">
-        <v>0.005532710280373832</v>
+        <v>-0</v>
       </c>
       <c r="R4">
-        <v>0.08176795580110496</v>
+        <v>-0</v>
       </c>
       <c r="S4">
         <v>0</v>
       </c>
-      <c r="T4">
-        <v>0</v>
-      </c>
       <c r="U4">
-        <v>14.3</v>
+        <v>0.001</v>
       </c>
       <c r="V4">
-        <v>0.2672897196261683</v>
-      </c>
-      <c r="W4">
-        <v>0.03573543928923988</v>
+        <v>7.199424046076314e-06</v>
       </c>
       <c r="X4">
-        <v>0.05240830515847517</v>
-      </c>
-      <c r="Y4">
-        <v>-0.01667286586923529</v>
-      </c>
-      <c r="Z4">
-        <v>0.03808975834292291</v>
-      </c>
-      <c r="AA4">
-        <v>0.03291038353011649</v>
+        <v>0.08639843809559511</v>
       </c>
       <c r="AB4">
-        <v>0.05240830515847517</v>
-      </c>
-      <c r="AC4">
-        <v>-0.01949792162835868</v>
+        <v>0.08459114577611394</v>
       </c>
       <c r="AD4">
-        <v>0</v>
+        <v>8.73</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>0</v>
+        <v>8.73</v>
       </c>
       <c r="AG4">
-        <v>-14.3</v>
+        <v>8.729000000000001</v>
       </c>
       <c r="AH4">
-        <v>0</v>
+        <v>0.05913432229221703</v>
       </c>
       <c r="AI4">
-        <v>0</v>
+        <v>0.07273181704573857</v>
       </c>
       <c r="AJ4">
-        <v>-0.3647959183673469</v>
+        <v>0.05912794911568865</v>
       </c>
       <c r="AK4">
-        <v>-0.1442986881937437</v>
+        <v>0.07272409167784454</v>
       </c>
       <c r="AL4">
-        <v>0</v>
+        <v>0.34</v>
       </c>
       <c r="AM4">
-        <v>0</v>
-      </c>
-      <c r="AN4">
-        <v>0</v>
-      </c>
-      <c r="AP4">
-        <v>-4.948096885813149</v>
+        <v>0.34</v>
+      </c>
+      <c r="AO4">
+        <v>19.5</v>
+      </c>
+      <c r="AQ4">
+        <v>19.5</v>
       </c>
     </row>
     <row r="5">
@@ -969,7 +918,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ECM Libra Group Berhad (KLSE:ECM)</t>
+          <t>OSK Ventures International Berhad (KLSE:OSKVI)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -977,101 +926,122 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="D5">
+        <v>-0.048</v>
+      </c>
+      <c r="E5">
+        <v>-0.049</v>
+      </c>
       <c r="G5">
-        <v>0</v>
+        <v>1.034586466165413</v>
       </c>
       <c r="H5">
-        <v>0</v>
+        <v>1.034586466165413</v>
       </c>
       <c r="I5">
-        <v>0</v>
+        <v>0.8406015037593985</v>
       </c>
       <c r="J5">
-        <v>0</v>
+        <v>0.8406015037593985</v>
       </c>
       <c r="K5">
-        <v>-4.55</v>
+        <v>5.78</v>
       </c>
       <c r="L5">
-        <v>-2.156398104265403</v>
+        <v>0.869172932330827</v>
       </c>
       <c r="M5">
-        <v>-0</v>
+        <v>0.845</v>
       </c>
       <c r="N5">
-        <v>-0</v>
+        <v>0.03626609442060086</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>0.1461937716262976</v>
       </c>
       <c r="P5">
-        <v>-0</v>
+        <v>0.845</v>
       </c>
       <c r="Q5">
-        <v>-0</v>
+        <v>0.03626609442060086</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>0.1461937716262976</v>
       </c>
       <c r="S5">
         <v>0</v>
       </c>
+      <c r="T5">
+        <v>0</v>
+      </c>
       <c r="U5">
-        <v>0.588</v>
+        <v>1.82</v>
       </c>
       <c r="V5">
-        <v>0.02840579710144928</v>
+        <v>0.07811158798283262</v>
       </c>
       <c r="W5">
-        <v>-0.09978070175438596</v>
+        <v>0.1199170124481328</v>
       </c>
       <c r="X5">
-        <v>0.0665169724425594</v>
+        <v>0.08429959409509402</v>
       </c>
       <c r="Y5">
-        <v>-0.1662976741969454</v>
+        <v>0.03561741835303876</v>
       </c>
       <c r="Z5">
-        <v>0.04113862351335543</v>
+        <v>0.1406663141195135</v>
       </c>
       <c r="AA5">
-        <v>0</v>
+        <v>0.1182443151771549</v>
       </c>
       <c r="AB5">
-        <v>0.05482486625658607</v>
+        <v>0.08424107708469629</v>
       </c>
       <c r="AC5">
-        <v>-0.05482486625658607</v>
+        <v>0.03400323809245866</v>
       </c>
       <c r="AD5">
-        <v>10.3</v>
+        <v>0.048</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>10.3</v>
+        <v>0.048</v>
       </c>
       <c r="AG5">
-        <v>9.712000000000002</v>
+        <v>-1.772</v>
       </c>
       <c r="AH5">
-        <v>0.332258064516129</v>
+        <v>0.002055850608189138</v>
       </c>
       <c r="AI5">
-        <v>0.2064128256513026</v>
+        <v>0.0009907529722589167</v>
       </c>
       <c r="AJ5">
-        <v>0.3193476259371301</v>
+        <v>-0.08231140839836491</v>
       </c>
       <c r="AK5">
-        <v>0.1969500324464633</v>
+        <v>-0.03800291670241057</v>
       </c>
       <c r="AL5">
-        <v>0</v>
+        <v>0.002</v>
       </c>
       <c r="AM5">
-        <v>0</v>
+        <v>0.002</v>
+      </c>
+      <c r="AN5">
+        <v>0.008556149732620321</v>
+      </c>
+      <c r="AO5">
+        <v>2795</v>
+      </c>
+      <c r="AP5">
+        <v>-0.3158645276292335</v>
+      </c>
+      <c r="AQ5">
+        <v>2795</v>
       </c>
     </row>
     <row r="6">
@@ -1082,7 +1052,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Fintec Global Berhad (KLSE:FINTEC)</t>
+          <t>Kuchai Development Berhad (KLSE:KUCHAI)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1090,113 +1060,113 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="D6">
+        <v>0.291</v>
+      </c>
       <c r="G6">
-        <v>-0.3777272727272727</v>
+        <v>0.7426900584795322</v>
       </c>
       <c r="H6">
-        <v>-0.3777272727272727</v>
+        <v>0.7426900584795322</v>
       </c>
       <c r="I6">
-        <v>-0.3831818181818182</v>
+        <v>0.7251461988304093</v>
       </c>
       <c r="J6">
-        <v>-0.3831818181818182</v>
+        <v>0.7251461988304093</v>
       </c>
       <c r="K6">
-        <v>-60.4</v>
+        <v>-24</v>
       </c>
       <c r="L6">
-        <v>-2.745454545454546</v>
+        <v>-14.03508771929825</v>
       </c>
       <c r="M6">
-        <v>-0</v>
+        <v>0.266</v>
       </c>
       <c r="N6">
-        <v>-0</v>
+        <v>0.007208672086720868</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <v>-0.01108333333333333</v>
       </c>
       <c r="P6">
-        <v>-0</v>
+        <v>0.266</v>
       </c>
       <c r="Q6">
-        <v>-0</v>
+        <v>0.007208672086720868</v>
       </c>
       <c r="R6">
-        <v>0</v>
+        <v>-0.01108333333333333</v>
       </c>
       <c r="S6">
         <v>0</v>
       </c>
+      <c r="T6">
+        <v>0</v>
+      </c>
       <c r="U6">
-        <v>4.7</v>
+        <v>14.5</v>
       </c>
       <c r="V6">
-        <v>0.3381294964028777</v>
+        <v>0.3929539295392954</v>
       </c>
       <c r="W6">
-        <v>-0.196870925684485</v>
+        <v>-0.2116402116402116</v>
       </c>
       <c r="X6">
-        <v>0.05259393410701906</v>
+        <v>0.08422846832151597</v>
       </c>
       <c r="Y6">
-        <v>-0.2494648597915041</v>
+        <v>-0.2958686799617276</v>
       </c>
       <c r="Z6">
-        <v>0.06972837627967418</v>
+        <v>0.01725529767911201</v>
       </c>
       <c r="AA6">
-        <v>-0.02671864600171152</v>
+        <v>0.01251261352169526</v>
       </c>
       <c r="AB6">
-        <v>0.05245561101222283</v>
+        <v>0.08422846832151597</v>
       </c>
       <c r="AC6">
-        <v>-0.07917425701393435</v>
+        <v>-0.07171585479982071</v>
       </c>
       <c r="AD6">
-        <v>0.091</v>
+        <v>0</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>0.091</v>
+        <v>0</v>
       </c>
       <c r="AG6">
-        <v>-4.609</v>
+        <v>-14.5</v>
       </c>
       <c r="AH6">
-        <v>0.006504181259381031</v>
+        <v>0</v>
       </c>
       <c r="AI6">
-        <v>0.001111233224652282</v>
+        <v>0</v>
       </c>
       <c r="AJ6">
-        <v>-0.496071467011086</v>
+        <v>-0.6473214285714286</v>
       </c>
       <c r="AK6">
-        <v>-0.05970903343654053</v>
+        <v>-0.2730696798493409</v>
       </c>
       <c r="AL6">
-        <v>0.29</v>
+        <v>0</v>
       </c>
       <c r="AM6">
-        <v>-1.38</v>
+        <v>0</v>
       </c>
       <c r="AN6">
-        <v>-0.01095066185318893</v>
-      </c>
-      <c r="AO6">
-        <v>-29.06896551724138</v>
+        <v>0</v>
       </c>
       <c r="AP6">
-        <v>0.554632972322503</v>
-      </c>
-      <c r="AQ6">
-        <v>6.108695652173913</v>
+        <v>-11.69354838709677</v>
       </c>
     </row>
     <row r="7">
@@ -1207,7 +1177,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Greenpro Capital Corp. (NasdaqCM:GRNQ)</t>
+          <t>ECM Libra Group Berhad (KLSE:ECM)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1215,26 +1185,23 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="D7">
-        <v>-0.0275</v>
-      </c>
       <c r="G7">
-        <v>-1.03921568627451</v>
+        <v>0</v>
       </c>
       <c r="H7">
-        <v>-1.03921568627451</v>
+        <v>0</v>
       </c>
       <c r="I7">
-        <v>-1.360217930814511</v>
+        <v>0</v>
       </c>
       <c r="J7">
-        <v>-1.360217930814511</v>
+        <v>0</v>
       </c>
       <c r="K7">
-        <v>-15.5</v>
+        <v>0.034</v>
       </c>
       <c r="L7">
-        <v>-6.07843137254902</v>
+        <v>0.007623318385650225</v>
       </c>
       <c r="M7">
         <v>-0</v>
@@ -1243,7 +1210,7 @@
         <v>-0</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P7">
         <v>-0</v>
@@ -1252,79 +1219,67 @@
         <v>-0</v>
       </c>
       <c r="R7">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S7">
         <v>0</v>
       </c>
       <c r="U7">
-        <v>6</v>
+        <v>0.463</v>
       </c>
       <c r="V7">
-        <v>0.1234567901234568</v>
+        <v>0.02280788177339901</v>
       </c>
       <c r="W7">
-        <v>-2.596314907872697</v>
+        <v>0.0008585858585858586</v>
       </c>
       <c r="X7">
-        <v>0.05255636520148443</v>
+        <v>0.09938233118289416</v>
       </c>
       <c r="Y7">
-        <v>-2.648871273074182</v>
+        <v>-0.0985237453243083</v>
       </c>
       <c r="Z7">
-        <v>0.3541775567467487</v>
+        <v>0.09044451654769629</v>
       </c>
       <c r="AA7">
-        <v>-0.4817586633790017</v>
+        <v>0</v>
       </c>
       <c r="AB7">
-        <v>0.05253237494509164</v>
+        <v>0.08521833319253803</v>
       </c>
       <c r="AC7">
-        <v>-0.5342910383240933</v>
+        <v>-0.08521833319253803</v>
       </c>
       <c r="AD7">
-        <v>0.171</v>
+        <v>8.91</v>
       </c>
       <c r="AE7">
-        <v>0.08277861788502039</v>
+        <v>0</v>
       </c>
       <c r="AF7">
-        <v>0.2537786178850204</v>
+        <v>8.91</v>
       </c>
       <c r="AG7">
-        <v>-5.74622138211498</v>
+        <v>8.447000000000001</v>
       </c>
       <c r="AH7">
-        <v>0.005194656893788639</v>
+        <v>0.3050325231085245</v>
       </c>
       <c r="AI7">
-        <v>0.01291245937074313</v>
+        <v>0.2052522460262612</v>
       </c>
       <c r="AJ7">
-        <v>-0.1340890247591095</v>
+        <v>0.2938393571503114</v>
       </c>
       <c r="AK7">
-        <v>-0.4208520983772238</v>
+        <v>0.1966842852818591</v>
       </c>
       <c r="AL7">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="AM7">
-        <v>13.993</v>
-      </c>
-      <c r="AN7">
-        <v>-0.05226161369193155</v>
-      </c>
-      <c r="AO7">
-        <v>-0.2528571428571428</v>
-      </c>
-      <c r="AP7">
-        <v>1.756180129008246</v>
-      </c>
-      <c r="AQ7">
-        <v>-0.2529836346744801</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1335,7 +1290,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Pimpinan Ehsan Berhad (KLSE:PEB)</t>
+          <t>Fintec Global Berhad (KLSE:FINTEC)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1343,8 +1298,23 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="G8">
+        <v>-1.399477806788512</v>
+      </c>
+      <c r="H8">
+        <v>-1.399477806788512</v>
+      </c>
+      <c r="I8">
+        <v>-1.378590078328982</v>
+      </c>
+      <c r="J8">
+        <v>-1.378590078328982</v>
+      </c>
       <c r="K8">
-        <v>-1.01</v>
+        <v>-29.8</v>
+      </c>
+      <c r="L8">
+        <v>-7.780678851174935</v>
       </c>
       <c r="M8">
         <v>-0</v>
@@ -1368,73 +1338,560 @@
         <v>0</v>
       </c>
       <c r="U8">
-        <v>16.3</v>
+        <v>1.35</v>
       </c>
       <c r="V8">
-        <v>0.6735537190082646</v>
+        <v>0.1</v>
       </c>
       <c r="W8">
-        <v>-0.05941176470588235</v>
+        <v>-0.3701863354037267</v>
       </c>
       <c r="X8">
-        <v>0.05251141174727678</v>
+        <v>0.08452513304501411</v>
       </c>
       <c r="Y8">
-        <v>-0.1119231764531591</v>
+        <v>-0.4547114684487408</v>
       </c>
       <c r="Z8">
-        <v>0</v>
+        <v>0.04932325404695368</v>
       </c>
       <c r="AA8">
-        <v>-3.832853025936624</v>
+        <v>-0.06799654866003015</v>
       </c>
       <c r="AB8">
-        <v>0.05243465713330331</v>
+        <v>0.08428071869288846</v>
       </c>
       <c r="AC8">
-        <v>-3.885287683069928</v>
+        <v>-0.1522772673529186</v>
       </c>
       <c r="AD8">
-        <v>0.08799999999999999</v>
+        <v>0.116</v>
       </c>
       <c r="AE8">
         <v>0</v>
       </c>
       <c r="AF8">
-        <v>0.08799999999999999</v>
+        <v>0.116</v>
       </c>
       <c r="AG8">
-        <v>-16.212</v>
+        <v>-1.234</v>
       </c>
       <c r="AH8">
-        <v>0.003623188405797101</v>
+        <v>0.008519388954171564</v>
       </c>
       <c r="AI8">
-        <v>0.005504128096072054</v>
+        <v>0.002488415994508324</v>
       </c>
       <c r="AJ8">
-        <v>-2.029544316474712</v>
+        <v>-0.100603293657264</v>
       </c>
       <c r="AK8">
-        <v>51.96153846153856</v>
+        <v>-0.02726107895550745</v>
       </c>
       <c r="AL8">
-        <v>0.003</v>
+        <v>0.041</v>
       </c>
       <c r="AM8">
-        <v>-0.318</v>
+        <v>-0.11</v>
       </c>
       <c r="AN8">
-        <v>-0.06769230769230769</v>
+        <v>-0.02261208576998051</v>
       </c>
       <c r="AO8">
-        <v>-443.3333333333334</v>
+        <v>-128.780487804878</v>
       </c>
       <c r="AP8">
-        <v>12.47076923076923</v>
+        <v>0.2405458089668616</v>
       </c>
       <c r="AQ8">
-        <v>4.182389937106918</v>
+        <v>48.00000000000001</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Malaysia</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Greenpro Capital Corp. (NasdaqCM:GRNQ)</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="D9">
+        <v>0.0107</v>
+      </c>
+      <c r="G9">
+        <v>-0.6762402088772845</v>
+      </c>
+      <c r="H9">
+        <v>-0.6762402088772845</v>
+      </c>
+      <c r="I9">
+        <v>-0.4538358892180567</v>
+      </c>
+      <c r="J9">
+        <v>-0.4538358892180567</v>
+      </c>
+      <c r="K9">
+        <v>-3.77</v>
+      </c>
+      <c r="L9">
+        <v>-0.9843342036553525</v>
+      </c>
+      <c r="M9">
+        <v>-0</v>
+      </c>
+      <c r="N9">
+        <v>-0</v>
+      </c>
+      <c r="O9">
+        <v>0</v>
+      </c>
+      <c r="P9">
+        <v>-0</v>
+      </c>
+      <c r="Q9">
+        <v>-0</v>
+      </c>
+      <c r="R9">
+        <v>0</v>
+      </c>
+      <c r="S9">
+        <v>0</v>
+      </c>
+      <c r="U9">
+        <v>3.61</v>
+      </c>
+      <c r="V9">
+        <v>0.4242068155111633</v>
+      </c>
+      <c r="W9">
+        <v>-0.1984210526315789</v>
+      </c>
+      <c r="X9">
+        <v>0.08463805871426505</v>
+      </c>
+      <c r="Y9">
+        <v>-0.283059111345844</v>
+      </c>
+      <c r="Z9">
+        <v>0.2963030062278539</v>
+      </c>
+      <c r="AA9">
+        <v>-0.1344729383094015</v>
+      </c>
+      <c r="AB9">
+        <v>0.08440106277443808</v>
+      </c>
+      <c r="AC9">
+        <v>-0.2188740010838396</v>
+      </c>
+      <c r="AD9">
+        <v>0</v>
+      </c>
+      <c r="AE9">
+        <v>0.1009572785257866</v>
+      </c>
+      <c r="AF9">
+        <v>0.1009572785257866</v>
+      </c>
+      <c r="AG9">
+        <v>-3.509042721474213</v>
+      </c>
+      <c r="AH9">
+        <v>0.01172428050218718</v>
+      </c>
+      <c r="AI9">
+        <v>0.006155572312719374</v>
+      </c>
+      <c r="AJ9">
+        <v>-0.7016742047651786</v>
+      </c>
+      <c r="AK9">
+        <v>-0.2743377719950172</v>
+      </c>
+      <c r="AL9">
+        <v>0.001</v>
+      </c>
+      <c r="AM9">
+        <v>-0.014</v>
+      </c>
+      <c r="AN9">
+        <v>-0</v>
+      </c>
+      <c r="AO9">
+        <v>-1810</v>
+      </c>
+      <c r="AP9">
+        <v>2.252273890548276</v>
+      </c>
+      <c r="AQ9">
+        <v>129.2857142857143</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Malaysia</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kairous Acquisition Corp. Limited (NasdaqGM:KACL)</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="K10">
+        <v>0.08</v>
+      </c>
+      <c r="M10">
+        <v>-0</v>
+      </c>
+      <c r="N10">
+        <v>-0</v>
+      </c>
+      <c r="O10">
+        <v>-0</v>
+      </c>
+      <c r="P10">
+        <v>-0</v>
+      </c>
+      <c r="Q10">
+        <v>-0</v>
+      </c>
+      <c r="R10">
+        <v>-0</v>
+      </c>
+      <c r="S10">
+        <v>0</v>
+      </c>
+      <c r="U10">
+        <v>0.341</v>
+      </c>
+      <c r="V10">
+        <v>0.00325071496663489</v>
+      </c>
+      <c r="W10">
+        <v>6.153846153846154</v>
+      </c>
+      <c r="X10">
+        <v>0.08425150735406797</v>
+      </c>
+      <c r="Y10">
+        <v>6.069594646492086</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+      <c r="AA10">
+        <v>-15</v>
+      </c>
+      <c r="AB10">
+        <v>0.08423255823176641</v>
+      </c>
+      <c r="AC10">
+        <v>-15.08423255823177</v>
+      </c>
+      <c r="AD10">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="AE10">
+        <v>0</v>
+      </c>
+      <c r="AF10">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="AG10">
+        <v>-0.271</v>
+      </c>
+      <c r="AH10">
+        <v>0.0006668571972944651</v>
+      </c>
+      <c r="AI10">
+        <v>-0.02966101694915254</v>
+      </c>
+      <c r="AJ10">
+        <v>-0.002590104082042264</v>
+      </c>
+      <c r="AK10">
+        <v>0.100333209922251</v>
+      </c>
+      <c r="AL10">
+        <v>0</v>
+      </c>
+      <c r="AM10">
+        <v>-0.47</v>
+      </c>
+      <c r="AQ10">
+        <v>0.8297872340425533</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Malaysia</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Energem Corp. (NasdaqGM:ENCP)</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="K11">
+        <v>-0.739</v>
+      </c>
+      <c r="M11">
+        <v>-0</v>
+      </c>
+      <c r="N11">
+        <v>-0</v>
+      </c>
+      <c r="O11">
+        <v>0</v>
+      </c>
+      <c r="P11">
+        <v>-0</v>
+      </c>
+      <c r="Q11">
+        <v>-0</v>
+      </c>
+      <c r="R11">
+        <v>0</v>
+      </c>
+      <c r="S11">
+        <v>0</v>
+      </c>
+      <c r="U11">
+        <v>0.051</v>
+      </c>
+      <c r="V11">
+        <v>0.0003315994798439531</v>
+      </c>
+      <c r="X11">
+        <v>0.08424844739562043</v>
+      </c>
+      <c r="AB11">
+        <v>0.08423201533928572</v>
+      </c>
+      <c r="AD11">
+        <v>0.089</v>
+      </c>
+      <c r="AE11">
+        <v>0</v>
+      </c>
+      <c r="AF11">
+        <v>0.089</v>
+      </c>
+      <c r="AG11">
+        <v>0.038</v>
+      </c>
+      <c r="AH11">
+        <v>0.0005783389326072688</v>
+      </c>
+      <c r="AI11">
+        <v>-0.02275632830478138</v>
+      </c>
+      <c r="AJ11">
+        <v>0.0002470130916938597</v>
+      </c>
+      <c r="AK11">
+        <v>-0.009591115598182735</v>
+      </c>
+      <c r="AL11">
+        <v>0</v>
+      </c>
+      <c r="AM11">
+        <v>-0.003</v>
+      </c>
+      <c r="AQ11">
+        <v>247.3333333333333</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Malaysia</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>DUET Acquisition Corp. (NasdaqGM:DUET)</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="K12">
+        <v>-0.006</v>
+      </c>
+      <c r="M12">
+        <v>-0</v>
+      </c>
+      <c r="N12">
+        <v>-0</v>
+      </c>
+      <c r="O12">
+        <v>0</v>
+      </c>
+      <c r="P12">
+        <v>-0</v>
+      </c>
+      <c r="Q12">
+        <v>-0</v>
+      </c>
+      <c r="R12">
+        <v>0</v>
+      </c>
+      <c r="S12">
+        <v>0</v>
+      </c>
+      <c r="U12">
+        <v>0.027</v>
+      </c>
+      <c r="V12">
+        <v>0.00024</v>
+      </c>
+      <c r="X12">
+        <v>0.08424381304859346</v>
+      </c>
+      <c r="AB12">
+        <v>0.08423119293837825</v>
+      </c>
+      <c r="AD12">
+        <v>0.05</v>
+      </c>
+      <c r="AE12">
+        <v>0</v>
+      </c>
+      <c r="AF12">
+        <v>0.05</v>
+      </c>
+      <c r="AG12">
+        <v>0.023</v>
+      </c>
+      <c r="AH12">
+        <v>0.000444247001332741</v>
+      </c>
+      <c r="AI12">
+        <v>-0.02358490566037736</v>
+      </c>
+      <c r="AJ12">
+        <v>0.0002044026554571066</v>
+      </c>
+      <c r="AK12">
+        <v>-0.01071262226362366</v>
+      </c>
+      <c r="AL12">
+        <v>0</v>
+      </c>
+      <c r="AM12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Malaysia</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>PHP Ventures Acquisition Corp. (NasdaqCM:PPHP)</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="K13">
+        <v>-1.99</v>
+      </c>
+      <c r="M13">
+        <v>-0</v>
+      </c>
+      <c r="N13">
+        <v>-0</v>
+      </c>
+      <c r="O13">
+        <v>0</v>
+      </c>
+      <c r="P13">
+        <v>-0</v>
+      </c>
+      <c r="Q13">
+        <v>-0</v>
+      </c>
+      <c r="R13">
+        <v>0</v>
+      </c>
+      <c r="S13">
+        <v>0</v>
+      </c>
+      <c r="U13">
+        <v>0.001</v>
+      </c>
+      <c r="V13">
+        <v>1.288659793814433e-05</v>
+      </c>
+      <c r="W13">
+        <v>1.592</v>
+      </c>
+      <c r="X13">
+        <v>0.0847223272889906</v>
+      </c>
+      <c r="Y13">
+        <v>1.50727767271101</v>
+      </c>
+      <c r="AB13">
+        <v>0.08419170494885977</v>
+      </c>
+      <c r="AD13">
+        <v>1.11</v>
+      </c>
+      <c r="AE13">
+        <v>0</v>
+      </c>
+      <c r="AF13">
+        <v>1.11</v>
+      </c>
+      <c r="AG13">
+        <v>1.109</v>
+      </c>
+      <c r="AH13">
+        <v>0.01410240121966714</v>
+      </c>
+      <c r="AI13">
+        <v>-0.4319066147859922</v>
+      </c>
+      <c r="AJ13">
+        <v>0.01408987536368141</v>
+      </c>
+      <c r="AK13">
+        <v>-0.4313496693893428</v>
+      </c>
+      <c r="AL13">
+        <v>0</v>
+      </c>
+      <c r="AM13">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/malaysia/malaysia_investments_asset_management.xlsx
+++ b/research/traditional_assets/database/data/malaysia/malaysia_investments_asset_management.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ13"/>
+  <dimension ref="A1:AQ14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,121 +588,115 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0107</v>
+        <v>0.105</v>
       </c>
       <c r="E2">
-        <v>-0.049</v>
+        <v>0.367</v>
       </c>
       <c r="G2">
-        <v>-0.02176776429809359</v>
+        <v>0.1266818700114025</v>
       </c>
       <c r="H2">
-        <v>-0.02176776429809359</v>
+        <v>0.1266818700114025</v>
       </c>
       <c r="I2">
-        <v>0.1082775925232181</v>
+        <v>-0.2400548902084215</v>
       </c>
       <c r="J2">
-        <v>0.1081579157146818</v>
+        <v>-0.2221734014290145</v>
       </c>
       <c r="K2">
-        <v>-47.686</v>
+        <v>21.979</v>
       </c>
       <c r="L2">
-        <v>-1.652894280762565</v>
+        <v>1.253078677309008</v>
       </c>
       <c r="M2">
-        <v>1.111</v>
+        <v>234.28</v>
       </c>
       <c r="N2">
-        <v>0.001564987111042245</v>
+        <v>0.4415878161872809</v>
       </c>
       <c r="O2">
-        <v>-0.02329824267080485</v>
+        <v>10.65926566267801</v>
       </c>
       <c r="P2">
-        <v>1.111</v>
+        <v>1.1</v>
       </c>
       <c r="Q2">
-        <v>0.001564987111042245</v>
+        <v>0.002073359218909036</v>
       </c>
       <c r="R2">
-        <v>-0.02329824267080485</v>
+        <v>0.05004777287410711</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>233.18</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>0.9953047635308179</v>
       </c>
       <c r="U2">
-        <v>35.664</v>
+        <v>36.462</v>
       </c>
       <c r="V2">
-        <v>0.05023735403079264</v>
+        <v>0.06872620349078297</v>
       </c>
       <c r="W2">
-        <v>0.0008585858585858586</v>
+        <v>0.05806389590091236</v>
       </c>
       <c r="X2">
-        <v>0.08434413796471429</v>
+        <v>0.0718338545510791</v>
       </c>
       <c r="Y2">
-        <v>-0.08348555210612843</v>
+        <v>-0.01376995865016674</v>
       </c>
       <c r="Z2">
-        <v>0.100771959569411</v>
-      </c>
-      <c r="AA2">
-        <v>-0.06799654866003015</v>
+        <v>0.1105147724808036</v>
       </c>
       <c r="AB2">
-        <v>0.08424107708469629</v>
-      </c>
-      <c r="AC2">
-        <v>-0.1522772673529186</v>
+        <v>0.07126702903894014</v>
       </c>
       <c r="AD2">
-        <v>19.189</v>
+        <v>14.126</v>
       </c>
       <c r="AE2">
-        <v>0.1009572785257866</v>
+        <v>0.01781387127856185</v>
       </c>
       <c r="AF2">
-        <v>19.28995727852579</v>
+        <v>14.14381387127856</v>
       </c>
       <c r="AG2">
-        <v>-16.37404272147421</v>
+        <v>-22.31818612872144</v>
       </c>
       <c r="AH2">
-        <v>0.02645359079630031</v>
+        <v>0.0259670170309505</v>
       </c>
       <c r="AI2">
-        <v>0.05571751150706224</v>
+        <v>0.07613295461146134</v>
       </c>
       <c r="AJ2">
-        <v>-0.02360950798532045</v>
+        <v>-0.04391426247275199</v>
       </c>
       <c r="AK2">
-        <v>-0.0527266330077789</v>
+        <v>-0.14946967471216</v>
       </c>
       <c r="AL2">
-        <v>0.387</v>
+        <v>0.031</v>
       </c>
       <c r="AM2">
-        <v>-0.578</v>
+        <v>-9.581999999999999</v>
       </c>
       <c r="AN2">
-        <v>93.15048543689295</v>
+        <v>3.208995910949569</v>
       </c>
       <c r="AO2">
-        <v>7.886304909560722</v>
+        <v>-136.3225806451613</v>
       </c>
       <c r="AP2">
-        <v>-79.48564427900082</v>
+        <v>-5.070010479037129</v>
       </c>
       <c r="AQ2">
-        <v>-5.280276816608996</v>
+        <v>0.4410352744729702</v>
       </c>
     </row>
     <row r="3">
@@ -713,7 +707,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Pimpinan Ehsan Berhad (KLSE:PEB)</t>
+          <t>OSK Ventures International Berhad (KLSE:OSKVI)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -721,89 +715,119 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="D3">
+        <v>1.185</v>
+      </c>
+      <c r="G3">
+        <v>0.6671874999999999</v>
+      </c>
+      <c r="H3">
+        <v>0.6671874999999999</v>
+      </c>
+      <c r="I3">
+        <v>0.8453125</v>
+      </c>
+      <c r="J3">
+        <v>0.8389805711610487</v>
+      </c>
       <c r="K3">
-        <v>0.325</v>
+        <v>5.3</v>
+      </c>
+      <c r="L3">
+        <v>0.8281249999999999</v>
       </c>
       <c r="M3">
-        <v>-0</v>
+        <v>0.837</v>
       </c>
       <c r="N3">
-        <v>-0</v>
+        <v>0.03623376623376623</v>
       </c>
       <c r="O3">
-        <v>-0</v>
+        <v>0.1579245283018868</v>
       </c>
       <c r="P3">
-        <v>-0</v>
+        <v>0.837</v>
       </c>
       <c r="Q3">
-        <v>-0</v>
+        <v>0.03623376623376623</v>
       </c>
       <c r="R3">
-        <v>-0</v>
+        <v>0.1579245283018868</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
       <c r="U3">
-        <v>13.5</v>
+        <v>0.04</v>
       </c>
       <c r="V3">
-        <v>0.6852791878172589</v>
+        <v>0.001731601731601732</v>
       </c>
       <c r="W3">
-        <v>0.02044025157232704</v>
+        <v>0.109504132231405</v>
       </c>
       <c r="X3">
-        <v>0.08434413796471429</v>
+        <v>0.07214354913332313</v>
       </c>
       <c r="Y3">
-        <v>-0.06390388639238725</v>
+        <v>0.03736058309808182</v>
+      </c>
+      <c r="Z3">
+        <v>0.137256584026765</v>
+      </c>
+      <c r="AA3">
+        <v>0.1151556072623898</v>
       </c>
       <c r="AB3">
-        <v>0.08424894719578287</v>
+        <v>0.07133657694994379</v>
+      </c>
+      <c r="AC3">
+        <v>0.04381903031244602</v>
       </c>
       <c r="AD3">
-        <v>0.066</v>
+        <v>0.819</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.066</v>
+        <v>0.819</v>
       </c>
       <c r="AG3">
-        <v>-13.434</v>
+        <v>0.7789999999999999</v>
       </c>
       <c r="AH3">
-        <v>0.003339067084893252</v>
+        <v>0.03424056189640035</v>
       </c>
       <c r="AI3">
-        <v>0.004500204554752489</v>
+        <v>0.01541821193923078</v>
       </c>
       <c r="AJ3">
-        <v>-2.143951484200447</v>
+        <v>0.03262280665019473</v>
       </c>
       <c r="AK3">
-        <v>-11.52144082332761</v>
+        <v>0.01467623730665612</v>
       </c>
       <c r="AL3">
-        <v>0.003</v>
+        <v>0.019</v>
       </c>
       <c r="AM3">
-        <v>-0.323</v>
+        <v>0.019</v>
       </c>
       <c r="AN3">
-        <v>1.5</v>
+        <v>0.150828729281768</v>
       </c>
       <c r="AO3">
-        <v>10</v>
+        <v>284.7368421052632</v>
       </c>
       <c r="AP3">
-        <v>-305.3181818181818</v>
+        <v>0.1434622467771639</v>
       </c>
       <c r="AQ3">
-        <v>-0.09287925696594426</v>
+        <v>284.7368421052632</v>
       </c>
     </row>
     <row r="4">
@@ -814,7 +838,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>AME Real Estate Investment Trust (KLSE:AMEREIT)</t>
+          <t>Kuchai Development Berhad (KLSE:KUCHAI)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -822,92 +846,116 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="D4">
+        <v>0.105</v>
+      </c>
+      <c r="E4">
+        <v>0.367</v>
+      </c>
       <c r="G4">
-        <v>0</v>
+        <v>0.5867158671586716</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>0.5867158671586716</v>
       </c>
       <c r="I4">
-        <v>0.7921146953405018</v>
+        <v>0.8302583025830258</v>
       </c>
       <c r="J4">
-        <v>0.7921146953405018</v>
+        <v>0.8183199479053614</v>
       </c>
       <c r="K4">
-        <v>6.4</v>
+        <v>6.03</v>
       </c>
       <c r="L4">
-        <v>0.7646356033452809</v>
+        <v>2.22509225092251</v>
       </c>
       <c r="M4">
-        <v>-0</v>
+        <v>0.263</v>
       </c>
       <c r="N4">
-        <v>-0</v>
+        <v>0.007804154302670623</v>
       </c>
       <c r="O4">
-        <v>-0</v>
+        <v>0.04361525704809287</v>
       </c>
       <c r="P4">
-        <v>-0</v>
+        <v>0.263</v>
       </c>
       <c r="Q4">
-        <v>-0</v>
+        <v>0.007804154302670623</v>
       </c>
       <c r="R4">
-        <v>-0</v>
+        <v>0.04361525704809287</v>
       </c>
       <c r="S4">
         <v>0</v>
       </c>
+      <c r="T4">
+        <v>0</v>
+      </c>
       <c r="U4">
-        <v>0.001</v>
+        <v>17.9</v>
       </c>
       <c r="V4">
-        <v>7.199424046076314e-06</v>
+        <v>0.5311572700296735</v>
+      </c>
+      <c r="W4">
+        <v>0.08920118343195267</v>
       </c>
       <c r="X4">
-        <v>0.08639843809559511</v>
+        <v>0.071268666165022</v>
+      </c>
+      <c r="Y4">
+        <v>0.01793251726693067</v>
+      </c>
+      <c r="Z4">
+        <v>0.05103578154425613</v>
+      </c>
+      <c r="AA4">
+        <v>0.04176359809460508</v>
       </c>
       <c r="AB4">
-        <v>0.08459114577611394</v>
+        <v>0.071268666165022</v>
+      </c>
+      <c r="AC4">
+        <v>-0.02950506807041692</v>
       </c>
       <c r="AD4">
-        <v>8.73</v>
+        <v>0</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>8.73</v>
+        <v>0</v>
       </c>
       <c r="AG4">
-        <v>8.729000000000001</v>
+        <v>-17.9</v>
       </c>
       <c r="AH4">
-        <v>0.05913432229221703</v>
+        <v>0</v>
       </c>
       <c r="AI4">
-        <v>0.07273181704573857</v>
+        <v>0</v>
       </c>
       <c r="AJ4">
-        <v>0.05912794911568865</v>
+        <v>-1.132911392405063</v>
       </c>
       <c r="AK4">
-        <v>0.07272409167784454</v>
+        <v>-0.3123909249563699</v>
       </c>
       <c r="AL4">
-        <v>0.34</v>
+        <v>0</v>
       </c>
       <c r="AM4">
-        <v>0.34</v>
-      </c>
-      <c r="AO4">
-        <v>19.5</v>
-      </c>
-      <c r="AQ4">
-        <v>19.5</v>
+        <v>0</v>
+      </c>
+      <c r="AN4">
+        <v>0</v>
+      </c>
+      <c r="AP4">
+        <v>-7.955555555555555</v>
       </c>
     </row>
     <row r="5">
@@ -918,7 +966,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>OSK Ventures International Berhad (KLSE:OSKVI)</t>
+          <t>Fintec Global Berhad (KLSE:FINTEC)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -926,122 +974,113 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="D5">
-        <v>-0.048</v>
-      </c>
-      <c r="E5">
-        <v>-0.049</v>
-      </c>
       <c r="G5">
-        <v>1.034586466165413</v>
+        <v>-0.377431906614786</v>
       </c>
       <c r="H5">
-        <v>1.034586466165413</v>
+        <v>-0.377431906614786</v>
       </c>
       <c r="I5">
-        <v>0.8406015037593985</v>
+        <v>-0.4105058365758755</v>
       </c>
       <c r="J5">
-        <v>0.8406015037593985</v>
+        <v>-0.4105058365758755</v>
       </c>
       <c r="K5">
-        <v>5.78</v>
+        <v>6.54</v>
       </c>
       <c r="L5">
-        <v>0.869172932330827</v>
+        <v>1.272373540856031</v>
       </c>
       <c r="M5">
-        <v>0.845</v>
+        <v>-0</v>
       </c>
       <c r="N5">
-        <v>0.03626609442060086</v>
+        <v>-0</v>
       </c>
       <c r="O5">
-        <v>0.1461937716262976</v>
+        <v>-0</v>
       </c>
       <c r="P5">
-        <v>0.845</v>
+        <v>-0</v>
       </c>
       <c r="Q5">
-        <v>0.03626609442060086</v>
+        <v>-0</v>
       </c>
       <c r="R5">
-        <v>0.1461937716262976</v>
+        <v>-0</v>
       </c>
       <c r="S5">
         <v>0</v>
       </c>
-      <c r="T5">
-        <v>0</v>
-      </c>
       <c r="U5">
-        <v>1.82</v>
+        <v>2.45</v>
       </c>
       <c r="V5">
-        <v>0.07811158798283262</v>
+        <v>0.189922480620155</v>
       </c>
       <c r="W5">
-        <v>0.1199170124481328</v>
+        <v>0.1440528634361234</v>
       </c>
       <c r="X5">
-        <v>0.08429959409509402</v>
+        <v>0.07130501093551989</v>
       </c>
       <c r="Y5">
-        <v>0.03561741835303876</v>
+        <v>0.07274785250060348</v>
       </c>
       <c r="Z5">
-        <v>0.1406663141195135</v>
+        <v>0.1123349943176851</v>
       </c>
       <c r="AA5">
-        <v>0.1182443151771549</v>
+        <v>-0.04611417081912755</v>
       </c>
       <c r="AB5">
-        <v>0.08424107708469629</v>
+        <v>0.07127456630283628</v>
       </c>
       <c r="AC5">
-        <v>0.03400323809245866</v>
+        <v>-0.1173887371219638</v>
       </c>
       <c r="AD5">
-        <v>0.048</v>
+        <v>0.019</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>0.048</v>
+        <v>0.019</v>
       </c>
       <c r="AG5">
-        <v>-1.772</v>
+        <v>-2.431</v>
       </c>
       <c r="AH5">
-        <v>0.002055850608189138</v>
+        <v>0.001470702066723431</v>
       </c>
       <c r="AI5">
-        <v>0.0009907529722589167</v>
+        <v>0.0003624639920639463</v>
       </c>
       <c r="AJ5">
-        <v>-0.08231140839836491</v>
+        <v>-0.2322093800745057</v>
       </c>
       <c r="AK5">
-        <v>-0.03800291670241057</v>
+        <v>-0.0486501631011227</v>
       </c>
       <c r="AL5">
-        <v>0.002</v>
+        <v>0.006</v>
       </c>
       <c r="AM5">
-        <v>0.002</v>
+        <v>0.006</v>
       </c>
       <c r="AN5">
-        <v>0.008556149732620321</v>
+        <v>-0.01038251366120218</v>
       </c>
       <c r="AO5">
-        <v>2795</v>
+        <v>-351.6666666666666</v>
       </c>
       <c r="AP5">
-        <v>-0.3158645276292335</v>
+        <v>1.328415300546448</v>
       </c>
       <c r="AQ5">
-        <v>2795</v>
+        <v>-351.6666666666666</v>
       </c>
     </row>
     <row r="6">
@@ -1052,7 +1091,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Kuchai Development Berhad (KLSE:KUCHAI)</t>
+          <t>Greenpro Capital Corp. (NasdaqCM:GRNQ)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1061,112 +1100,112 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.291</v>
+        <v>-0.0704</v>
       </c>
       <c r="G6">
-        <v>0.7426900584795322</v>
+        <v>-0.4133738601823708</v>
       </c>
       <c r="H6">
-        <v>0.7426900584795322</v>
+        <v>-0.4133738601823708</v>
       </c>
       <c r="I6">
-        <v>0.7251461988304093</v>
+        <v>-0.369168016491098</v>
       </c>
       <c r="J6">
-        <v>0.7251461988304093</v>
+        <v>-0.3682179517427753</v>
       </c>
       <c r="K6">
-        <v>-24</v>
+        <v>2.74</v>
       </c>
       <c r="L6">
-        <v>-14.03508771929825</v>
+        <v>0.8328267477203648</v>
       </c>
       <c r="M6">
-        <v>0.266</v>
+        <v>-0</v>
       </c>
       <c r="N6">
-        <v>0.007208672086720868</v>
+        <v>-0</v>
       </c>
       <c r="O6">
-        <v>-0.01108333333333333</v>
+        <v>-0</v>
       </c>
       <c r="P6">
-        <v>0.266</v>
+        <v>-0</v>
       </c>
       <c r="Q6">
-        <v>0.007208672086720868</v>
+        <v>-0</v>
       </c>
       <c r="R6">
-        <v>-0.01108333333333333</v>
+        <v>-0</v>
       </c>
       <c r="S6">
         <v>0</v>
       </c>
-      <c r="T6">
-        <v>0</v>
-      </c>
       <c r="U6">
-        <v>14.5</v>
+        <v>2.5</v>
       </c>
       <c r="V6">
-        <v>0.3929539295392954</v>
+        <v>0.2796420581655481</v>
       </c>
       <c r="W6">
-        <v>-0.2116402116402116</v>
+        <v>0.17125</v>
       </c>
       <c r="X6">
-        <v>0.08422846832151597</v>
+        <v>0.0713647594058482</v>
       </c>
       <c r="Y6">
-        <v>-0.2958686799617276</v>
+        <v>0.09988524059415181</v>
       </c>
       <c r="Z6">
-        <v>0.01725529767911201</v>
+        <v>0.2727616289813679</v>
       </c>
       <c r="AA6">
-        <v>0.01251261352169526</v>
+        <v>-0.1004357283375421</v>
       </c>
       <c r="AB6">
-        <v>0.08422846832151597</v>
+        <v>0.07128422812599795</v>
       </c>
       <c r="AC6">
-        <v>-0.07171585479982071</v>
+        <v>-0.17171995646354</v>
       </c>
       <c r="AD6">
-        <v>0</v>
+        <v>0.017</v>
       </c>
       <c r="AE6">
-        <v>0</v>
+        <v>0.01781387127856185</v>
       </c>
       <c r="AF6">
-        <v>0</v>
+        <v>0.03481387127856185</v>
       </c>
       <c r="AG6">
-        <v>-14.5</v>
+        <v>-2.465186128721438</v>
       </c>
       <c r="AH6">
-        <v>0</v>
+        <v>0.003879063318513393</v>
       </c>
       <c r="AI6">
-        <v>0</v>
+        <v>0.002941649244104315</v>
       </c>
       <c r="AJ6">
-        <v>-0.6473214285714286</v>
+        <v>-0.3807346709465558</v>
       </c>
       <c r="AK6">
-        <v>-0.2730696798493409</v>
+        <v>-0.2640851936326598</v>
       </c>
       <c r="AL6">
         <v>0</v>
       </c>
       <c r="AM6">
-        <v>0</v>
+        <v>-0.041</v>
       </c>
       <c r="AN6">
-        <v>0</v>
+        <v>-0.01587301587301587</v>
       </c>
       <c r="AP6">
-        <v>-11.69354838709677</v>
+        <v>2.301761091243173</v>
+      </c>
+      <c r="AQ6">
+        <v>30</v>
       </c>
     </row>
     <row r="7">
@@ -1177,7 +1216,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ECM Libra Group Berhad (KLSE:ECM)</t>
+          <t>Pimpinan Ehsan Berhad (KLSE:PEB)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1185,23 +1224,8 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="G7">
-        <v>0</v>
-      </c>
-      <c r="H7">
-        <v>0</v>
-      </c>
-      <c r="I7">
-        <v>0</v>
-      </c>
-      <c r="J7">
-        <v>0</v>
-      </c>
       <c r="K7">
-        <v>0.034</v>
-      </c>
-      <c r="L7">
-        <v>0.007623318385650225</v>
+        <v>0.1</v>
       </c>
       <c r="M7">
         <v>-0</v>
@@ -1225,61 +1249,73 @@
         <v>0</v>
       </c>
       <c r="U7">
-        <v>0.463</v>
+        <v>13.2</v>
       </c>
       <c r="V7">
-        <v>0.02280788177339901</v>
+        <v>0.6839378238341969</v>
       </c>
       <c r="W7">
-        <v>0.0008585858585858586</v>
+        <v>0.006849315068493151</v>
       </c>
       <c r="X7">
-        <v>0.09938233118289416</v>
+        <v>0.07130190869576919</v>
       </c>
       <c r="Y7">
-        <v>-0.0985237453243083</v>
+        <v>-0.06445259362727604</v>
       </c>
       <c r="Z7">
-        <v>0.09044451654769629</v>
+        <v>0</v>
       </c>
       <c r="AA7">
-        <v>0</v>
+        <v>-0.2114529503665424</v>
       </c>
       <c r="AB7">
-        <v>0.08521833319253803</v>
+        <v>0.07126539191285827</v>
       </c>
       <c r="AC7">
-        <v>-0.08521833319253803</v>
+        <v>-0.2827183422794007</v>
       </c>
       <c r="AD7">
-        <v>8.91</v>
+        <v>0.026</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>8.91</v>
+        <v>0.026</v>
       </c>
       <c r="AG7">
-        <v>8.447000000000001</v>
+        <v>-13.174</v>
       </c>
       <c r="AH7">
-        <v>0.3050325231085245</v>
+        <v>0.001345337886784642</v>
       </c>
       <c r="AI7">
-        <v>0.2052522460262612</v>
+        <v>0.00177765622863394</v>
       </c>
       <c r="AJ7">
-        <v>0.2938393571503114</v>
+        <v>-2.150506039830231</v>
       </c>
       <c r="AK7">
-        <v>0.1966842852818591</v>
+        <v>-9.238429172510518</v>
       </c>
       <c r="AL7">
-        <v>0</v>
+        <v>0.006</v>
       </c>
       <c r="AM7">
-        <v>0</v>
+        <v>-0.526</v>
+      </c>
+      <c r="AN7">
+        <v>-0.06896551724137931</v>
+      </c>
+      <c r="AO7">
+        <v>-65.16666666666667</v>
+      </c>
+      <c r="AP7">
+        <v>34.94429708222812</v>
+      </c>
+      <c r="AQ7">
+        <v>0.7433460076045627</v>
       </c>
     </row>
     <row r="8">
@@ -1290,7 +1326,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Fintec Global Berhad (KLSE:FINTEC)</t>
+          <t>Evergreen Corporation (NasdaqGM:EVGR)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1298,32 +1334,17 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="G8">
-        <v>-1.399477806788512</v>
-      </c>
-      <c r="H8">
-        <v>-1.399477806788512</v>
-      </c>
-      <c r="I8">
-        <v>-1.378590078328982</v>
-      </c>
-      <c r="J8">
-        <v>-1.378590078328982</v>
-      </c>
       <c r="K8">
-        <v>-29.8</v>
-      </c>
-      <c r="L8">
-        <v>-7.780678851174935</v>
+        <v>1.03</v>
       </c>
       <c r="M8">
-        <v>-0</v>
+        <v>43.1</v>
       </c>
       <c r="N8">
-        <v>-0</v>
+        <v>0.3532786885245902</v>
       </c>
       <c r="O8">
-        <v>0</v>
+        <v>41.84466019417476</v>
       </c>
       <c r="P8">
         <v>-0</v>
@@ -1332,79 +1353,64 @@
         <v>-0</v>
       </c>
       <c r="R8">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>43.1</v>
+      </c>
+      <c r="T8">
+        <v>1</v>
       </c>
       <c r="U8">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="V8">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W8">
-        <v>-0.3701863354037267</v>
+        <v>-0.288515406162465</v>
       </c>
       <c r="X8">
-        <v>0.08452513304501411</v>
+        <v>0.07185523124885568</v>
       </c>
       <c r="Y8">
-        <v>-0.4547114684487408</v>
-      </c>
-      <c r="Z8">
-        <v>0.04932325404695368</v>
-      </c>
-      <c r="AA8">
-        <v>-0.06799654866003015</v>
+        <v>-0.3603706374113207</v>
       </c>
       <c r="AB8">
-        <v>0.08428071869288846</v>
-      </c>
-      <c r="AC8">
-        <v>-0.1522772673529186</v>
+        <v>0.0712121573357381</v>
       </c>
       <c r="AD8">
-        <v>0.116</v>
+        <v>2.9</v>
       </c>
       <c r="AE8">
         <v>0</v>
       </c>
       <c r="AF8">
-        <v>0.116</v>
+        <v>2.9</v>
       </c>
       <c r="AG8">
-        <v>-1.234</v>
+        <v>2.9</v>
       </c>
       <c r="AH8">
-        <v>0.008519388954171564</v>
+        <v>0.02321857485988791</v>
       </c>
       <c r="AI8">
-        <v>0.002488415994508324</v>
+        <v>-0.6904761904761906</v>
       </c>
       <c r="AJ8">
-        <v>-0.100603293657264</v>
+        <v>0.02321857485988791</v>
       </c>
       <c r="AK8">
-        <v>-0.02726107895550745</v>
+        <v>-0.6904761904761906</v>
       </c>
       <c r="AL8">
-        <v>0.041</v>
+        <v>0</v>
       </c>
       <c r="AM8">
-        <v>-0.11</v>
-      </c>
-      <c r="AN8">
-        <v>-0.02261208576998051</v>
-      </c>
-      <c r="AO8">
-        <v>-128.780487804878</v>
-      </c>
-      <c r="AP8">
-        <v>0.2405458089668616</v>
+        <v>-1.24</v>
       </c>
       <c r="AQ8">
-        <v>48.00000000000001</v>
+        <v>0.1701612903225806</v>
       </c>
     </row>
     <row r="9">
@@ -1415,7 +1421,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Greenpro Capital Corp. (NasdaqCM:GRNQ)</t>
+          <t>DUET Acquisition Corp. (NasdaqGM:DUET)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1423,35 +1429,17 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="D9">
-        <v>0.0107</v>
-      </c>
-      <c r="G9">
-        <v>-0.6762402088772845</v>
-      </c>
-      <c r="H9">
-        <v>-0.6762402088772845</v>
-      </c>
-      <c r="I9">
-        <v>-0.4538358892180567</v>
-      </c>
-      <c r="J9">
-        <v>-0.4538358892180567</v>
-      </c>
       <c r="K9">
-        <v>-3.77</v>
-      </c>
-      <c r="L9">
-        <v>-0.9843342036553525</v>
+        <v>-0.068</v>
       </c>
       <c r="M9">
-        <v>-0</v>
+        <v>36.3</v>
       </c>
       <c r="N9">
-        <v>-0</v>
+        <v>0.4300947867298577</v>
       </c>
       <c r="O9">
-        <v>0</v>
+        <v>-533.8235294117646</v>
       </c>
       <c r="P9">
         <v>-0</v>
@@ -1463,76 +1451,61 @@
         <v>0</v>
       </c>
       <c r="S9">
-        <v>0</v>
+        <v>36.3</v>
+      </c>
+      <c r="T9">
+        <v>1</v>
       </c>
       <c r="U9">
-        <v>3.61</v>
+        <v>0.172</v>
       </c>
       <c r="V9">
-        <v>0.4242068155111633</v>
+        <v>0.002037914691943128</v>
       </c>
       <c r="W9">
-        <v>-0.1984210526315789</v>
+        <v>0.03133640552995392</v>
       </c>
       <c r="X9">
-        <v>0.08463805871426505</v>
+        <v>0.07181247785330251</v>
       </c>
       <c r="Y9">
-        <v>-0.283059111345844</v>
-      </c>
-      <c r="Z9">
-        <v>0.2963030062278539</v>
-      </c>
-      <c r="AA9">
-        <v>-0.1344729383094015</v>
+        <v>-0.04047607232334859</v>
       </c>
       <c r="AB9">
-        <v>0.08440106277443808</v>
-      </c>
-      <c r="AC9">
-        <v>-0.2188740010838396</v>
+        <v>0.07135517111186969</v>
       </c>
       <c r="AD9">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AE9">
-        <v>0.1009572785257866</v>
+        <v>0</v>
       </c>
       <c r="AF9">
-        <v>0.1009572785257866</v>
+        <v>1.86</v>
       </c>
       <c r="AG9">
-        <v>-3.509042721474213</v>
+        <v>1.688</v>
       </c>
       <c r="AH9">
-        <v>0.01172428050218718</v>
+        <v>0.02156271736610248</v>
       </c>
       <c r="AI9">
-        <v>0.006155572312719374</v>
+        <v>-1.563025210084034</v>
       </c>
       <c r="AJ9">
-        <v>-0.7016742047651786</v>
+        <v>0.0196078431372549</v>
       </c>
       <c r="AK9">
-        <v>-0.2743377719950172</v>
+        <v>-1.239353891336271</v>
       </c>
       <c r="AL9">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="AM9">
-        <v>-0.014</v>
-      </c>
-      <c r="AN9">
-        <v>-0</v>
-      </c>
-      <c r="AO9">
-        <v>-1810</v>
-      </c>
-      <c r="AP9">
-        <v>2.252273890548276</v>
+        <v>-2.86</v>
       </c>
       <c r="AQ9">
-        <v>129.2857142857143</v>
+        <v>0.8111888111888111</v>
       </c>
     </row>
     <row r="10">
@@ -1543,7 +1516,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Kairous Acquisition Corp. Limited (NasdaqGM:KACL)</t>
+          <t>Technology &amp; Telecommunication Acquisition Corporation (NasdaqGM:TETE)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1552,16 +1525,16 @@
         </is>
       </c>
       <c r="K10">
-        <v>0.08</v>
+        <v>1.45</v>
       </c>
       <c r="M10">
-        <v>-0</v>
+        <v>88</v>
       </c>
       <c r="N10">
-        <v>-0</v>
+        <v>1.197278911564626</v>
       </c>
       <c r="O10">
-        <v>-0</v>
+        <v>60.68965517241379</v>
       </c>
       <c r="P10">
         <v>-0</v>
@@ -1573,67 +1546,61 @@
         <v>-0</v>
       </c>
       <c r="S10">
-        <v>0</v>
+        <v>88</v>
+      </c>
+      <c r="T10">
+        <v>1</v>
       </c>
       <c r="U10">
-        <v>0.341</v>
+        <v>0.039</v>
       </c>
       <c r="V10">
-        <v>0.00325071496663489</v>
+        <v>0.0005306122448979592</v>
       </c>
       <c r="W10">
-        <v>6.153846153846154</v>
+        <v>-0.4215116279069767</v>
       </c>
       <c r="X10">
-        <v>0.08425150735406797</v>
+        <v>0.07177226180349988</v>
       </c>
       <c r="Y10">
-        <v>6.069594646492086</v>
-      </c>
-      <c r="Z10">
-        <v>0</v>
-      </c>
-      <c r="AA10">
-        <v>-15</v>
+        <v>-0.4932838897104766</v>
       </c>
       <c r="AB10">
-        <v>0.08423255823176641</v>
-      </c>
-      <c r="AC10">
-        <v>-15.08423255823177</v>
+        <v>0.07121999062862502</v>
       </c>
       <c r="AD10">
-        <v>0.07000000000000001</v>
+        <v>1.5</v>
       </c>
       <c r="AE10">
         <v>0</v>
       </c>
       <c r="AF10">
-        <v>0.07000000000000001</v>
+        <v>1.5</v>
       </c>
       <c r="AG10">
-        <v>-0.271</v>
+        <v>1.461</v>
       </c>
       <c r="AH10">
-        <v>0.0006668571972944651</v>
+        <v>0.02</v>
       </c>
       <c r="AI10">
-        <v>-0.02966101694915254</v>
+        <v>-0.3588516746411484</v>
       </c>
       <c r="AJ10">
-        <v>-0.002590104082042264</v>
+        <v>0.01949013487013247</v>
       </c>
       <c r="AK10">
-        <v>0.100333209922251</v>
+        <v>-0.3462905901872482</v>
       </c>
       <c r="AL10">
         <v>0</v>
       </c>
       <c r="AM10">
-        <v>-0.47</v>
+        <v>-2.44</v>
       </c>
       <c r="AQ10">
-        <v>0.8297872340425533</v>
+        <v>0.4061475409836066</v>
       </c>
     </row>
     <row r="11">
@@ -1653,16 +1620,16 @@
         </is>
       </c>
       <c r="K11">
-        <v>-0.739</v>
+        <v>0.126</v>
       </c>
       <c r="M11">
-        <v>-0</v>
+        <v>7.48</v>
       </c>
       <c r="N11">
-        <v>-0</v>
+        <v>0.1430210325047801</v>
       </c>
       <c r="O11">
-        <v>0</v>
+        <v>59.36507936507937</v>
       </c>
       <c r="P11">
         <v>-0</v>
@@ -1671,55 +1638,64 @@
         <v>-0</v>
       </c>
       <c r="R11">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S11">
-        <v>0</v>
+        <v>7.48</v>
+      </c>
+      <c r="T11">
+        <v>1</v>
       </c>
       <c r="U11">
-        <v>0.051</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="V11">
-        <v>0.0003315994798439531</v>
+        <v>0.001663479923518164</v>
+      </c>
+      <c r="W11">
+        <v>-0.0315</v>
       </c>
       <c r="X11">
-        <v>0.08424844739562043</v>
+        <v>0.07188203217211647</v>
+      </c>
+      <c r="Y11">
+        <v>-0.1033820321721165</v>
       </c>
       <c r="AB11">
-        <v>0.08423201533928572</v>
+        <v>0.07120963799588387</v>
       </c>
       <c r="AD11">
-        <v>0.089</v>
+        <v>1.3</v>
       </c>
       <c r="AE11">
         <v>0</v>
       </c>
       <c r="AF11">
-        <v>0.089</v>
+        <v>1.3</v>
       </c>
       <c r="AG11">
-        <v>0.038</v>
+        <v>1.213</v>
       </c>
       <c r="AH11">
-        <v>0.0005783389326072688</v>
+        <v>0.02425373134328359</v>
       </c>
       <c r="AI11">
-        <v>-0.02275632830478138</v>
+        <v>-0.2748414376321353</v>
       </c>
       <c r="AJ11">
-        <v>0.0002470130916938597</v>
+        <v>0.02266738923252294</v>
       </c>
       <c r="AK11">
-        <v>-0.009591115598182735</v>
+        <v>-0.2518164832883538</v>
       </c>
       <c r="AL11">
         <v>0</v>
       </c>
       <c r="AM11">
-        <v>-0.003</v>
+        <v>-1.18</v>
       </c>
       <c r="AQ11">
-        <v>247.3333333333333</v>
+        <v>0.8898305084745763</v>
       </c>
     </row>
     <row r="12">
@@ -1730,7 +1706,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>DUET Acquisition Corp. (NasdaqGM:DUET)</t>
+          <t>Kairous Acquisition Corp. Limited (NasdaqGM:KACL)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1739,16 +1715,16 @@
         </is>
       </c>
       <c r="K12">
-        <v>-0.006</v>
+        <v>0.234</v>
       </c>
       <c r="M12">
-        <v>-0</v>
+        <v>58.3</v>
       </c>
       <c r="N12">
-        <v>-0</v>
+        <v>1.147637795275591</v>
       </c>
       <c r="O12">
-        <v>0</v>
+        <v>249.1452991452991</v>
       </c>
       <c r="P12">
         <v>-0</v>
@@ -1757,52 +1733,64 @@
         <v>-0</v>
       </c>
       <c r="R12">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S12">
-        <v>0</v>
+        <v>58.3</v>
+      </c>
+      <c r="T12">
+        <v>1</v>
       </c>
       <c r="U12">
-        <v>0.027</v>
+        <v>0.003</v>
       </c>
       <c r="V12">
-        <v>0.00024</v>
+        <v>5.905511811023623e-05</v>
+      </c>
+      <c r="W12">
+        <v>-0.0962962962962963</v>
       </c>
       <c r="X12">
-        <v>0.08424381304859346</v>
+        <v>0.07213330418840863</v>
+      </c>
+      <c r="Y12">
+        <v>-0.1684296004847049</v>
       </c>
       <c r="AB12">
-        <v>0.08423119293837825</v>
+        <v>0.07118627508972092</v>
       </c>
       <c r="AD12">
-        <v>0.05</v>
+        <v>1.78</v>
       </c>
       <c r="AE12">
         <v>0</v>
       </c>
       <c r="AF12">
-        <v>0.05</v>
+        <v>1.78</v>
       </c>
       <c r="AG12">
-        <v>0.023</v>
+        <v>1.777</v>
       </c>
       <c r="AH12">
-        <v>0.000444247001332741</v>
+        <v>0.03385317611259034</v>
       </c>
       <c r="AI12">
-        <v>-0.02358490566037736</v>
+        <v>-0.6054421768707484</v>
       </c>
       <c r="AJ12">
-        <v>0.0002044026554571066</v>
+        <v>0.0337980485763737</v>
       </c>
       <c r="AK12">
-        <v>-0.01071262226362366</v>
+        <v>-0.6038056405028883</v>
       </c>
       <c r="AL12">
         <v>0</v>
       </c>
       <c r="AM12">
-        <v>0</v>
+        <v>-1.32</v>
+      </c>
+      <c r="AQ12">
+        <v>0.8257575757575758</v>
       </c>
     </row>
     <row r="13">
@@ -1822,7 +1810,7 @@
         </is>
       </c>
       <c r="K13">
-        <v>-1.99</v>
+        <v>-1.44</v>
       </c>
       <c r="M13">
         <v>-0</v>
@@ -1846,51 +1834,140 @@
         <v>0</v>
       </c>
       <c r="U13">
-        <v>0.001</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="V13">
-        <v>1.288659793814433e-05</v>
+        <v>0.002431506849315068</v>
       </c>
       <c r="W13">
-        <v>1.592</v>
+        <v>0.3913043478260869</v>
       </c>
       <c r="X13">
-        <v>0.0847223272889906</v>
+        <v>0.07390529976812131</v>
       </c>
       <c r="Y13">
-        <v>1.50727767271101</v>
+        <v>0.3173990480579656</v>
       </c>
       <c r="AB13">
-        <v>0.08419170494885977</v>
+        <v>0.07103372236310594</v>
       </c>
       <c r="AD13">
-        <v>1.11</v>
+        <v>3.12</v>
       </c>
       <c r="AE13">
         <v>0</v>
       </c>
       <c r="AF13">
-        <v>1.11</v>
+        <v>3.12</v>
       </c>
       <c r="AG13">
-        <v>1.109</v>
+        <v>3.049</v>
       </c>
       <c r="AH13">
-        <v>0.01410240121966714</v>
+        <v>0.09653465346534654</v>
       </c>
       <c r="AI13">
-        <v>-0.4319066147859922</v>
+        <v>-0.75</v>
       </c>
       <c r="AJ13">
-        <v>0.01408987536368141</v>
+        <v>0.09454556730441253</v>
       </c>
       <c r="AK13">
-        <v>-0.4313496693893428</v>
+        <v>-0.720633419995273</v>
       </c>
       <c r="AL13">
         <v>0</v>
       </c>
       <c r="AM13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Malaysia</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Xenous Holdings, Inc. (OTCPK:XITO)</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="K14">
+        <v>-0.063</v>
+      </c>
+      <c r="M14">
+        <v>-0</v>
+      </c>
+      <c r="N14">
+        <v>-0</v>
+      </c>
+      <c r="O14">
+        <v>0</v>
+      </c>
+      <c r="P14">
+        <v>-0</v>
+      </c>
+      <c r="Q14">
+        <v>-0</v>
+      </c>
+      <c r="R14">
+        <v>0</v>
+      </c>
+      <c r="S14">
+        <v>0</v>
+      </c>
+      <c r="U14">
+        <v>0</v>
+      </c>
+      <c r="V14">
+        <v>0</v>
+      </c>
+      <c r="W14">
+        <v>0.0847913862718708</v>
+      </c>
+      <c r="X14">
+        <v>0.07221821549022063</v>
+      </c>
+      <c r="Y14">
+        <v>0.01257317078165017</v>
+      </c>
+      <c r="AB14">
+        <v>0.07141732086393252</v>
+      </c>
+      <c r="AD14">
+        <v>0.785</v>
+      </c>
+      <c r="AE14">
+        <v>0</v>
+      </c>
+      <c r="AF14">
+        <v>0.785</v>
+      </c>
+      <c r="AG14">
+        <v>0.785</v>
+      </c>
+      <c r="AH14">
+        <v>0.0370545197073401</v>
+      </c>
+      <c r="AI14">
+        <v>-37.38095238095235</v>
+      </c>
+      <c r="AJ14">
+        <v>0.0370545197073401</v>
+      </c>
+      <c r="AK14">
+        <v>-37.38095238095235</v>
+      </c>
+      <c r="AL14">
+        <v>0</v>
+      </c>
+      <c r="AM14">
         <v>0</v>
       </c>
     </row>
